--- a/data/trans_bre/P15A-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P15A-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 2,54</t>
+          <t>-2,25; 2,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 2,38</t>
+          <t>-3,12; 2,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 1,81</t>
+          <t>-2,6; 1,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 2,88</t>
+          <t>0,2; 3,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-68,08; 153,38</t>
+          <t>-66,41; 188,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-75,07; 136,34</t>
+          <t>-76,69; 147,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-72,68; 174,93</t>
+          <t>-75,74; 165,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 637,85</t>
+          <t>-8,27; 590,82</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 0,1</t>
+          <t>-4,58; 0,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 0,35</t>
+          <t>-3,73; 0,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 4,41</t>
+          <t>-0,37; 4,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 0,38</t>
+          <t>-3,98; 0,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-89,54; 13,07</t>
+          <t>-86,76; 30,02</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-92,33; 51,13</t>
+          <t>-92,92; 75,26</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-45,3; 519,86</t>
+          <t>-27,27; 586,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-84,63; 42,57</t>
+          <t>-83,93; 29,34</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 1,34</t>
+          <t>-5,27; 1,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 2,31</t>
+          <t>-2,68; 2,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 5,99</t>
+          <t>-0,46; 6,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 4,57</t>
+          <t>-0,98; 4,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-82,79; 47,24</t>
+          <t>-84,11; 32,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-75,59; 144,55</t>
+          <t>-78,88; 132,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-48,24; 488,2</t>
+          <t>-36,41; 570,5</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-31,03; 526,45</t>
+          <t>-32,62; 515,96</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,31</t>
+          <t>-1,18; 2,26</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 0,72</t>
+          <t>-2,31; 0,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 0,13</t>
+          <t>-2,32; 0,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 0,94</t>
+          <t>-1,94; 0,95</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,97; 99,62</t>
+          <t>-31,14; 85,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-63,31; 31,31</t>
+          <t>-62,51; 28,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-78,78; 13,66</t>
+          <t>-79,06; 8,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-62,3; 52,94</t>
+          <t>-66,14; 55,68</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 2,71</t>
+          <t>-2,72; 2,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,82</t>
+          <t>-1,2; 2,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 1,25</t>
+          <t>-2,76; 1,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 2,01</t>
+          <t>-3,38; 1,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-43,33; 139,63</t>
+          <t>-50,08; 133,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-34,96; 203,32</t>
+          <t>-32,47; 160,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-56,58; 53,63</t>
+          <t>-56,76; 47,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-56,49; 97,61</t>
+          <t>-56,93; 86,24</t>
         </is>
       </c>
     </row>
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,54; -0,81</t>
+          <t>-6,42; -0,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 2,76</t>
+          <t>-1,37; 2,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 0,16</t>
+          <t>-5,81; 0,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 3,13</t>
+          <t>-1,64; 3,12</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-78,37; -20,1</t>
+          <t>-78,14; -18,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-39,55; 218,3</t>
+          <t>-33,28; 231,23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-73,34; 7,36</t>
+          <t>-71,79; 11,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,87; -0,1</t>
+          <t>-1,8; -0,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 0,67</t>
+          <t>-0,92; 0,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,62</t>
+          <t>-0,83; 0,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,26</t>
+          <t>-0,47; 1,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-44,84; -2,22</t>
+          <t>-42,5; -0,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-28,07; 27,99</t>
+          <t>-27,84; 30,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-30,61; 26,6</t>
+          <t>-27,5; 33,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-18,39; 76,89</t>
+          <t>-18,84; 72,67</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P15A-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P15A-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,6</t>
+          <t>1,83</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>157,09%</t>
+          <t>166,57%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 2,77</t>
+          <t>-2,32; 2,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 2,53</t>
+          <t>-3,41; 2,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 1,66</t>
+          <t>-2,25; 1,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,2; 3,04</t>
+          <t>0,31; 3,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-66,41; 188,88</t>
+          <t>-69,27; 159,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-76,69; 147,52</t>
+          <t>-76,71; 144,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-75,74; 165,63</t>
+          <t>-73,51; 185,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 590,82</t>
+          <t>4,31; 587,96</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,26</t>
+          <t>-1,28</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-48,76%</t>
+          <t>-48,36%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,58; 0,23</t>
+          <t>-5,09; -0,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 0,39</t>
+          <t>-3,71; 0,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 4,55</t>
+          <t>-0,47; 4,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 0,29</t>
+          <t>-3,65; 0,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-86,76; 30,02</t>
+          <t>-91,01; 15,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-92,92; 75,26</t>
+          <t>-92,98; 83,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-27,27; 586,37</t>
+          <t>-31,76; 533,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-83,93; 29,34</t>
+          <t>-83,14; 29,95</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,28</t>
+          <t>-0,18</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>-5,77%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,27; 1,18</t>
+          <t>-5,04; 1,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 2,17</t>
+          <t>-2,43; 2,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 6,91</t>
+          <t>-0,57; 6,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 4,19</t>
+          <t>-2,92; 2,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-84,11; 32,76</t>
+          <t>-81,2; 46,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-78,88; 132,16</t>
+          <t>-76,04; 153,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-36,41; 570,5</t>
+          <t>-32,45; 559,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-32,62; 515,96</t>
+          <t>-66,2; 116,78</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>0,05</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-12,05%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 2,26</t>
+          <t>-1,41; 2,05</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 0,65</t>
+          <t>-2,39; 0,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 0,06</t>
+          <t>-2,22; 0,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 0,95</t>
+          <t>-1,24; 1,44</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,14; 85,05</t>
+          <t>-37,79; 84,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-62,51; 28,24</t>
+          <t>-62,13; 28,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-79,06; 8,4</t>
+          <t>-79,42; 16,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-66,14; 55,68</t>
+          <t>-42,7; 78,55</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,22</t>
+          <t>0,49</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-6,07%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 2,7</t>
+          <t>-2,44; 2,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 2,54</t>
+          <t>-1,2; 2,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 1,19</t>
+          <t>-2,95; 0,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 1,9</t>
+          <t>-2,48; 2,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-50,08; 133,99</t>
+          <t>-43,65; 122,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-32,47; 160,86</t>
+          <t>-35,03; 164,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-56,76; 47,37</t>
+          <t>-58,15; 35,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-56,93; 86,24</t>
+          <t>-47,15; 131,95</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,72</t>
+          <t>1,38</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>181,26%</t>
+          <t>130,75%</t>
         </is>
       </c>
     </row>
@@ -1160,37 +1160,37 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,42; -0,72</t>
+          <t>-6,38; -0,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 2,72</t>
+          <t>-1,68; 2,92</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 0,21</t>
+          <t>-5,39; 0,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 3,12</t>
+          <t>-2,25; 2,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-78,14; -18,47</t>
+          <t>-77,7; -17,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-33,28; 231,23</t>
+          <t>-39,88; 300,72</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-71,79; 11,09</t>
+          <t>-71,26; 12,07</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t>0,33</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,8; -0,04</t>
+          <t>-1,81; -0,07</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,73</t>
+          <t>-0,91; 0,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,7</t>
+          <t>-0,98; 0,61</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,47; 1,22</t>
+          <t>-0,4; 1,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-42,5; -0,67</t>
+          <t>-42,27; -2,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-27,84; 30,58</t>
+          <t>-28,22; 29,41</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-27,5; 33,11</t>
+          <t>-33,37; 26,86</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-18,84; 72,67</t>
+          <t>-14,91; 58,05</t>
         </is>
       </c>
     </row>
